--- a/Result/profitability/3532.xlsx
+++ b/Result/profitability/3532.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.45875</v>
+        <v>0.4175</v>
       </c>
       <c r="N2" t="n">
-        <v>17.72125</v>
+        <v>15.80625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.51</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4662500000000001</v>
+        <v>0.35375</v>
       </c>
       <c r="N3" t="n">
-        <v>19.05125</v>
+        <v>17.235</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.45625</v>
+        <v>0.395</v>
       </c>
       <c r="N4" t="n">
-        <v>21.39375</v>
+        <v>20.035</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,13 +1018,13 @@
         <v>0.44</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4350000000000001</v>
+        <v>0.4975</v>
       </c>
       <c r="N5" t="n">
-        <v>23.74125</v>
+        <v>22.80125</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.53</v>
       </c>
       <c r="M6" t="n">
-        <v>0.41625</v>
+        <v>0.36125</v>
       </c>
       <c r="N6" t="n">
-        <v>16.16875</v>
+        <v>15.10625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.24</v>
       </c>
       <c r="M7" t="n">
-        <v>0.31625</v>
+        <v>0.23375</v>
       </c>
       <c r="N7" t="n">
-        <v>14.48125</v>
+        <v>13.8875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.16</v>
       </c>
       <c r="M8" t="n">
-        <v>0.19875</v>
+        <v>0.23625</v>
       </c>
       <c r="N8" t="n">
-        <v>12.51875</v>
+        <v>13.2775</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3610</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3361</v>
+      </c>
+      <c r="E75" t="n">
+        <v>249</v>
+      </c>
+      <c r="F75" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G75" t="n">
+        <v>95</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.64%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-35</v>
+      </c>
+      <c r="J75" t="n">
+        <v>60</v>
+      </c>
+      <c r="K75" t="n">
+        <v>48</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3725000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.8275</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>7.313253012048193</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.315789473684211</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-7.52</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.521497919556172</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
